--- a/data/stocks_20260415_111654.xlsx
+++ b/data/stocks_20260415_111654.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,69 +1119,69 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>252</v>
+        <v>496.98</v>
       </c>
       <c r="D10" t="n">
-        <v>1.29</v>
+        <v>-4.43</v>
       </c>
       <c r="E10" t="n">
-        <v>240.97</v>
+        <v>508.44</v>
       </c>
       <c r="F10" t="n">
-        <v>229.8</v>
+        <v>486.58</v>
       </c>
       <c r="G10" t="n">
-        <v>223.59</v>
+        <v>471.22</v>
       </c>
       <c r="H10" t="n">
-        <v>1.893</v>
+        <v>25.358</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.107</v>
+        <v>21.844</v>
       </c>
       <c r="J10" t="n">
-        <v>76.90000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="K10" t="n">
-        <v>69.81</v>
+        <v>71.97</v>
       </c>
       <c r="L10" t="n">
-        <v>91.08</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>82.8</v>
+        <v>54.91</v>
       </c>
       <c r="N10" t="n">
-        <v>67.11</v>
+        <v>58.76</v>
       </c>
       <c r="O10" t="n">
-        <v>57.68</v>
+        <v>58.09</v>
       </c>
       <c r="P10" t="n">
-        <v>3629.23</v>
+        <v>4606.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2189.64</v>
+        <v>3980.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>251.89</v>
+        <v>525.02</v>
       </c>
       <c r="T10" t="n">
-        <v>261.3</v>
+        <v>534</v>
       </c>
       <c r="U10" t="n">
-        <v>248.19</v>
+        <v>490.02</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
@@ -1192,69 +1192,69 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>496.98</v>
+        <v>330.66</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.43</v>
+        <v>-4.39</v>
       </c>
       <c r="E11" t="n">
-        <v>508.44</v>
+        <v>346.66</v>
       </c>
       <c r="F11" t="n">
-        <v>486.58</v>
+        <v>337.76</v>
       </c>
       <c r="G11" t="n">
-        <v>471.22</v>
+        <v>323.86</v>
       </c>
       <c r="H11" t="n">
-        <v>25.358</v>
+        <v>10.443</v>
       </c>
       <c r="I11" t="n">
-        <v>21.844</v>
+        <v>9.628</v>
       </c>
       <c r="J11" t="n">
-        <v>71.95</v>
+        <v>59.32</v>
       </c>
       <c r="K11" t="n">
-        <v>71.97</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>71.90000000000001</v>
+        <v>41.34</v>
       </c>
       <c r="M11" t="n">
-        <v>54.91</v>
+        <v>45.71</v>
       </c>
       <c r="N11" t="n">
-        <v>58.76</v>
+        <v>51.42</v>
       </c>
       <c r="O11" t="n">
-        <v>58.09</v>
+        <v>54.25</v>
       </c>
       <c r="P11" t="n">
-        <v>4606.46</v>
+        <v>4151.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>3980.25</v>
+        <v>3681.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>525.02</v>
+        <v>345.84</v>
       </c>
       <c r="T11" t="n">
-        <v>534</v>
+        <v>347.99</v>
       </c>
       <c r="U11" t="n">
-        <v>490.02</v>
+        <v>327.5</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
@@ -1265,69 +1265,69 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300394</v>
+        <v>988</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>330.66</v>
+        <v>112.3</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.39</v>
+        <v>-6.91</v>
       </c>
       <c r="E12" t="n">
-        <v>346.66</v>
+        <v>117.79</v>
       </c>
       <c r="F12" t="n">
-        <v>337.76</v>
+        <v>111.22</v>
       </c>
       <c r="G12" t="n">
-        <v>323.86</v>
+        <v>111.47</v>
       </c>
       <c r="H12" t="n">
-        <v>10.443</v>
+        <v>3.487</v>
       </c>
       <c r="I12" t="n">
-        <v>9.628</v>
+        <v>3.227</v>
       </c>
       <c r="J12" t="n">
-        <v>59.32</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>68.31999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="L12" t="n">
-        <v>41.34</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>45.71</v>
+        <v>47.71</v>
       </c>
       <c r="N12" t="n">
-        <v>51.42</v>
+        <v>51.74</v>
       </c>
       <c r="O12" t="n">
-        <v>54.25</v>
+        <v>54.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4151.24</v>
+        <v>13478.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>3681.95</v>
+        <v>9835.040000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>345.84</v>
+        <v>120.39</v>
       </c>
       <c r="T12" t="n">
-        <v>347.99</v>
+        <v>120.39</v>
       </c>
       <c r="U12" t="n">
-        <v>327.5</v>
+        <v>110.6</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
@@ -1338,69 +1338,69 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>988</v>
+        <v>603986</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>112.3</v>
+        <v>274</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.91</v>
+        <v>-2.15</v>
       </c>
       <c r="E13" t="n">
-        <v>117.79</v>
+        <v>266.35</v>
       </c>
       <c r="F13" t="n">
-        <v>111.22</v>
+        <v>258.84</v>
       </c>
       <c r="G13" t="n">
-        <v>111.47</v>
+        <v>266.68</v>
       </c>
       <c r="H13" t="n">
-        <v>3.487</v>
+        <v>-4.324</v>
       </c>
       <c r="I13" t="n">
-        <v>3.227</v>
+        <v>-7.006</v>
       </c>
       <c r="J13" t="n">
-        <v>69.23999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="K13" t="n">
-        <v>65.84</v>
+        <v>63.05</v>
       </c>
       <c r="L13" t="n">
-        <v>76.04000000000001</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>47.71</v>
+        <v>61.08</v>
       </c>
       <c r="N13" t="n">
-        <v>51.74</v>
+        <v>53.16</v>
       </c>
       <c r="O13" t="n">
-        <v>54.7</v>
+        <v>50.99</v>
       </c>
       <c r="P13" t="n">
-        <v>13478.92</v>
+        <v>3969.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>9835.040000000001</v>
+        <v>3638.07</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="S13" t="n">
-        <v>120.39</v>
+        <v>285</v>
       </c>
       <c r="T13" t="n">
-        <v>120.39</v>
+        <v>287.65</v>
       </c>
       <c r="U13" t="n">
-        <v>110.6</v>
+        <v>271.98</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
@@ -1411,69 +1411,69 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603986</v>
+        <v>300042</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>274</v>
+        <v>48.77</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.15</v>
+        <v>-5.85</v>
       </c>
       <c r="E14" t="n">
-        <v>266.35</v>
+        <v>49.11</v>
       </c>
       <c r="F14" t="n">
-        <v>258.84</v>
+        <v>46.09</v>
       </c>
       <c r="G14" t="n">
-        <v>266.68</v>
+        <v>47.49</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.324</v>
+        <v>2.133</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.006</v>
+        <v>1.974</v>
       </c>
       <c r="J14" t="n">
-        <v>73.39</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>63.05</v>
+        <v>68.59</v>
       </c>
       <c r="L14" t="n">
-        <v>94.06999999999999</v>
+        <v>95.86</v>
       </c>
       <c r="M14" t="n">
-        <v>61.08</v>
+        <v>57.16</v>
       </c>
       <c r="N14" t="n">
-        <v>53.16</v>
+        <v>57.25</v>
       </c>
       <c r="O14" t="n">
-        <v>50.99</v>
+        <v>58.1</v>
       </c>
       <c r="P14" t="n">
-        <v>3969.73</v>
+        <v>3331.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>3638.07</v>
+        <v>3307.27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="S14" t="n">
-        <v>285</v>
+        <v>51.02</v>
       </c>
       <c r="T14" t="n">
-        <v>287.65</v>
+        <v>51.7</v>
       </c>
       <c r="U14" t="n">
-        <v>271.98</v>
+        <v>48.47</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
@@ -1484,69 +1484,69 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688525</v>
+        <v>300302</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>285.41</v>
+        <v>22.74</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.93</v>
+        <v>-3.03</v>
       </c>
       <c r="E15" t="n">
-        <v>259.68</v>
+        <v>22.63</v>
       </c>
       <c r="F15" t="n">
-        <v>238.22</v>
+        <v>21.25</v>
       </c>
       <c r="G15" t="n">
-        <v>237.68</v>
+        <v>21.95</v>
       </c>
       <c r="H15" t="n">
-        <v>16.294</v>
+        <v>0.503</v>
       </c>
       <c r="I15" t="n">
-        <v>11.766</v>
+        <v>0.308</v>
       </c>
       <c r="J15" t="n">
-        <v>80.06999999999999</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>64.26000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="L15" t="n">
-        <v>111.69</v>
+        <v>108.32</v>
       </c>
       <c r="M15" t="n">
-        <v>82.17</v>
+        <v>62.12</v>
       </c>
       <c r="N15" t="n">
-        <v>72.2</v>
+        <v>57.99</v>
       </c>
       <c r="O15" t="n">
-        <v>67.17</v>
+        <v>55.99</v>
       </c>
       <c r="P15" t="n">
-        <v>3983.34</v>
+        <v>2742.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>3901.55</v>
+        <v>4746.19</v>
       </c>
       <c r="R15" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="S15" t="n">
-        <v>290.19</v>
+        <v>23.45</v>
       </c>
       <c r="T15" t="n">
-        <v>292.18</v>
+        <v>23.5</v>
       </c>
       <c r="U15" t="n">
-        <v>278.16</v>
+        <v>22.62</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
@@ -1557,69 +1557,69 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300042</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>深华发A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48.77</v>
+        <v>15.73</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.85</v>
+        <v>-1.87</v>
       </c>
       <c r="E16" t="n">
-        <v>49.11</v>
+        <v>15.8</v>
       </c>
       <c r="F16" t="n">
-        <v>46.09</v>
+        <v>15.63</v>
       </c>
       <c r="G16" t="n">
-        <v>47.49</v>
+        <v>17.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.133</v>
+        <v>-0.175</v>
       </c>
       <c r="I16" t="n">
-        <v>1.974</v>
+        <v>-0.001</v>
       </c>
       <c r="J16" t="n">
-        <v>77.68000000000001</v>
+        <v>64.86</v>
       </c>
       <c r="K16" t="n">
-        <v>68.59</v>
+        <v>48.61</v>
       </c>
       <c r="L16" t="n">
-        <v>95.86</v>
+        <v>97.36</v>
       </c>
       <c r="M16" t="n">
-        <v>57.16</v>
+        <v>43.44</v>
       </c>
       <c r="N16" t="n">
-        <v>57.25</v>
+        <v>46.01</v>
       </c>
       <c r="O16" t="n">
-        <v>58.1</v>
+        <v>49.06</v>
       </c>
       <c r="P16" t="n">
-        <v>3331.95</v>
+        <v>593.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>3307.27</v>
+        <v>1461.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.01</v>
+        <v>0.41</v>
       </c>
       <c r="S16" t="n">
-        <v>51.02</v>
+        <v>15.98</v>
       </c>
       <c r="T16" t="n">
-        <v>51.7</v>
+        <v>16.03</v>
       </c>
       <c r="U16" t="n">
-        <v>48.47</v>
+        <v>15.66</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
@@ -1630,69 +1630,69 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>300302</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.74</v>
+        <v>40.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.03</v>
+        <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>22.63</v>
+        <v>40.1</v>
       </c>
       <c r="F17" t="n">
-        <v>21.25</v>
+        <v>38.73</v>
       </c>
       <c r="G17" t="n">
-        <v>21.95</v>
+        <v>38.19</v>
       </c>
       <c r="H17" t="n">
-        <v>0.503</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.308</v>
+        <v>0.321</v>
       </c>
       <c r="J17" t="n">
-        <v>80.93000000000001</v>
+        <v>81.13</v>
       </c>
       <c r="K17" t="n">
-        <v>67.23</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>108.32</v>
+        <v>94.17</v>
       </c>
       <c r="M17" t="n">
-        <v>62.12</v>
+        <v>61.72</v>
       </c>
       <c r="N17" t="n">
-        <v>57.99</v>
+        <v>57.64</v>
       </c>
       <c r="O17" t="n">
-        <v>55.99</v>
+        <v>55.32</v>
       </c>
       <c r="P17" t="n">
-        <v>2742.32</v>
+        <v>6422.92</v>
       </c>
       <c r="Q17" t="n">
-        <v>4746.19</v>
+        <v>6779.11</v>
       </c>
       <c r="R17" t="n">
-        <v>0.58</v>
+        <v>0.95</v>
       </c>
       <c r="S17" t="n">
-        <v>23.45</v>
+        <v>41.3</v>
       </c>
       <c r="T17" t="n">
-        <v>23.5</v>
+        <v>41.3</v>
       </c>
       <c r="U17" t="n">
-        <v>22.62</v>
+        <v>40</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
@@ -1703,69 +1703,69 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>300017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深华发A</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.73</v>
+        <v>18.26</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.87</v>
+        <v>-2.2</v>
       </c>
       <c r="E18" t="n">
-        <v>15.8</v>
+        <v>18.16</v>
       </c>
       <c r="F18" t="n">
-        <v>15.63</v>
+        <v>17.61</v>
       </c>
       <c r="G18" t="n">
-        <v>17.2</v>
+        <v>17.59</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.175</v>
+        <v>0.099</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.001</v>
+        <v>-0.023</v>
       </c>
       <c r="J18" t="n">
-        <v>64.86</v>
+        <v>69.14</v>
       </c>
       <c r="K18" t="n">
-        <v>48.61</v>
+        <v>62.47</v>
       </c>
       <c r="L18" t="n">
-        <v>97.36</v>
+        <v>82.47</v>
       </c>
       <c r="M18" t="n">
-        <v>43.44</v>
+        <v>56.99</v>
       </c>
       <c r="N18" t="n">
-        <v>46.01</v>
+        <v>53.49</v>
       </c>
       <c r="O18" t="n">
-        <v>49.06</v>
+        <v>53.72</v>
       </c>
       <c r="P18" t="n">
-        <v>593.33</v>
+        <v>25549.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1461.91</v>
+        <v>21905.8</v>
       </c>
       <c r="R18" t="n">
-        <v>0.41</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
-        <v>15.98</v>
+        <v>18.55</v>
       </c>
       <c r="T18" t="n">
-        <v>16.03</v>
+        <v>19.14</v>
       </c>
       <c r="U18" t="n">
-        <v>15.66</v>
+        <v>17.95</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
@@ -1776,69 +1776,69 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>603881</v>
+        <v>300418</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40.3</v>
+        <v>49.79</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.16</v>
+        <v>-2.08</v>
       </c>
       <c r="E19" t="n">
-        <v>40.1</v>
+        <v>50.18</v>
       </c>
       <c r="F19" t="n">
-        <v>38.73</v>
+        <v>49.59</v>
       </c>
       <c r="G19" t="n">
-        <v>38.19</v>
+        <v>50.23</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6929999999999999</v>
+        <v>-0.848</v>
       </c>
       <c r="I19" t="n">
-        <v>0.321</v>
+        <v>-1.097</v>
       </c>
       <c r="J19" t="n">
-        <v>81.13</v>
+        <v>61.14</v>
       </c>
       <c r="K19" t="n">
-        <v>74.59999999999999</v>
+        <v>55.67</v>
       </c>
       <c r="L19" t="n">
-        <v>94.17</v>
+        <v>72.08</v>
       </c>
       <c r="M19" t="n">
-        <v>61.72</v>
+        <v>48.45</v>
       </c>
       <c r="N19" t="n">
-        <v>57.64</v>
+        <v>47.49</v>
       </c>
       <c r="O19" t="n">
-        <v>55.32</v>
+        <v>48.26</v>
       </c>
       <c r="P19" t="n">
-        <v>6422.92</v>
+        <v>4392.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>6779.11</v>
+        <v>6173.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="S19" t="n">
-        <v>41.3</v>
+        <v>51.34</v>
       </c>
       <c r="T19" t="n">
-        <v>41.3</v>
+        <v>51.35</v>
       </c>
       <c r="U19" t="n">
-        <v>40</v>
+        <v>49.53</v>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
@@ -1849,69 +1849,69 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>300017</v>
+        <v>2230</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18.26</v>
+        <v>47.54</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2</v>
+        <v>-1.63</v>
       </c>
       <c r="E20" t="n">
-        <v>18.16</v>
+        <v>47.7</v>
       </c>
       <c r="F20" t="n">
-        <v>17.61</v>
+        <v>47.06</v>
       </c>
       <c r="G20" t="n">
-        <v>17.59</v>
+        <v>47.42</v>
       </c>
       <c r="H20" t="n">
-        <v>0.099</v>
+        <v>-1.225</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.023</v>
+        <v>-1.659</v>
       </c>
       <c r="J20" t="n">
-        <v>69.14</v>
+        <v>70.13</v>
       </c>
       <c r="K20" t="n">
-        <v>62.47</v>
+        <v>62.85</v>
       </c>
       <c r="L20" t="n">
-        <v>82.47</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>56.99</v>
+        <v>50.77</v>
       </c>
       <c r="N20" t="n">
-        <v>53.49</v>
+        <v>44.25</v>
       </c>
       <c r="O20" t="n">
-        <v>53.72</v>
+        <v>42.23</v>
       </c>
       <c r="P20" t="n">
-        <v>25549.25</v>
+        <v>3597.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>21905.8</v>
+        <v>3152.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S20" t="n">
-        <v>18.55</v>
+        <v>48.86</v>
       </c>
       <c r="T20" t="n">
-        <v>19.14</v>
+        <v>48.98</v>
       </c>
       <c r="U20" t="n">
-        <v>17.95</v>
+        <v>47.39</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
@@ -1922,69 +1922,69 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>300418</v>
+        <v>300058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>49.79</v>
+        <v>16.43</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.08</v>
+        <v>-4.86</v>
       </c>
       <c r="E21" t="n">
-        <v>50.18</v>
+        <v>16.68</v>
       </c>
       <c r="F21" t="n">
-        <v>49.59</v>
+        <v>15.51</v>
       </c>
       <c r="G21" t="n">
-        <v>50.23</v>
+        <v>14.98</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.848</v>
+        <v>0.08</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.097</v>
+        <v>-0.331</v>
       </c>
       <c r="J21" t="n">
-        <v>61.14</v>
+        <v>79.52</v>
       </c>
       <c r="K21" t="n">
-        <v>55.67</v>
+        <v>71.83</v>
       </c>
       <c r="L21" t="n">
-        <v>72.08</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>48.45</v>
+        <v>59.83</v>
       </c>
       <c r="N21" t="n">
-        <v>47.49</v>
+        <v>56.06</v>
       </c>
       <c r="O21" t="n">
-        <v>48.26</v>
+        <v>52.51</v>
       </c>
       <c r="P21" t="n">
-        <v>4392.67</v>
+        <v>50335.01</v>
       </c>
       <c r="Q21" t="n">
-        <v>6173.64</v>
+        <v>34550.21</v>
       </c>
       <c r="R21" t="n">
-        <v>0.71</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>51.34</v>
+        <v>17.13</v>
       </c>
       <c r="T21" t="n">
-        <v>51.35</v>
+        <v>17.4</v>
       </c>
       <c r="U21" t="n">
-        <v>49.53</v>
+        <v>16.31</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
@@ -1995,69 +1995,69 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2230</v>
+        <v>300496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47.54</v>
+        <v>60.52</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.63</v>
+        <v>-1.64</v>
       </c>
       <c r="E22" t="n">
-        <v>47.7</v>
+        <v>60.51</v>
       </c>
       <c r="F22" t="n">
-        <v>47.06</v>
+        <v>59.45</v>
       </c>
       <c r="G22" t="n">
-        <v>47.42</v>
+        <v>60.35</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.225</v>
+        <v>-1.87</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.659</v>
+        <v>-2.499</v>
       </c>
       <c r="J22" t="n">
-        <v>70.13</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>62.85</v>
+        <v>62.53</v>
       </c>
       <c r="L22" t="n">
-        <v>84.68000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>50.77</v>
+        <v>52.47</v>
       </c>
       <c r="N22" t="n">
-        <v>44.25</v>
+        <v>45.42</v>
       </c>
       <c r="O22" t="n">
-        <v>42.23</v>
+        <v>42.78</v>
       </c>
       <c r="P22" t="n">
-        <v>3597.9</v>
+        <v>957.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>3152.75</v>
+        <v>997.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.14</v>
+        <v>0.96</v>
       </c>
       <c r="S22" t="n">
-        <v>48.86</v>
+        <v>62</v>
       </c>
       <c r="T22" t="n">
-        <v>48.98</v>
+        <v>62.25</v>
       </c>
       <c r="U22" t="n">
-        <v>47.39</v>
+        <v>60.25</v>
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
@@ -2068,69 +2068,69 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>300058</v>
+        <v>547</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>航天发展</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.43</v>
+        <v>27.67</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.86</v>
+        <v>1.84</v>
       </c>
       <c r="E23" t="n">
-        <v>16.68</v>
+        <v>26.91</v>
       </c>
       <c r="F23" t="n">
-        <v>15.51</v>
+        <v>26.87</v>
       </c>
       <c r="G23" t="n">
-        <v>14.98</v>
+        <v>27.57</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08</v>
+        <v>-0.765</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.331</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>79.52</v>
+        <v>45.91</v>
       </c>
       <c r="K23" t="n">
-        <v>71.83</v>
+        <v>36.36</v>
       </c>
       <c r="L23" t="n">
-        <v>94.90000000000001</v>
+        <v>65.03</v>
       </c>
       <c r="M23" t="n">
-        <v>59.83</v>
+        <v>56.82</v>
       </c>
       <c r="N23" t="n">
-        <v>56.06</v>
+        <v>48.73</v>
       </c>
       <c r="O23" t="n">
-        <v>52.51</v>
+        <v>48.21</v>
       </c>
       <c r="P23" t="n">
-        <v>50335.01</v>
+        <v>24317.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>34550.21</v>
+        <v>18020.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>17.13</v>
+        <v>27.18</v>
       </c>
       <c r="T23" t="n">
-        <v>17.4</v>
+        <v>28.57</v>
       </c>
       <c r="U23" t="n">
-        <v>16.31</v>
+        <v>26.97</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
@@ -2141,69 +2141,69 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>300496</v>
+        <v>2202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>60.52</v>
+        <v>25.02</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.64</v>
+        <v>-1.11</v>
       </c>
       <c r="E24" t="n">
-        <v>60.51</v>
+        <v>24.47</v>
       </c>
       <c r="F24" t="n">
-        <v>59.45</v>
+        <v>24.28</v>
       </c>
       <c r="G24" t="n">
-        <v>60.35</v>
+        <v>26.28</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.87</v>
+        <v>-0.965</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.499</v>
+        <v>-0.83</v>
       </c>
       <c r="J24" t="n">
-        <v>73.26000000000001</v>
+        <v>46.94</v>
       </c>
       <c r="K24" t="n">
-        <v>62.53</v>
+        <v>30.58</v>
       </c>
       <c r="L24" t="n">
-        <v>94.70999999999999</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>52.47</v>
+        <v>50.43</v>
       </c>
       <c r="N24" t="n">
-        <v>45.42</v>
+        <v>44.3</v>
       </c>
       <c r="O24" t="n">
-        <v>42.78</v>
+        <v>47</v>
       </c>
       <c r="P24" t="n">
-        <v>957.63</v>
+        <v>25813.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>997.05</v>
+        <v>23761.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="S24" t="n">
-        <v>62</v>
+        <v>25.43</v>
       </c>
       <c r="T24" t="n">
-        <v>62.25</v>
+        <v>25.95</v>
       </c>
       <c r="U24" t="n">
-        <v>60.25</v>
+        <v>24.84</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
@@ -2214,69 +2214,69 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>547</v>
+        <v>301128</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.67</v>
+        <v>177.86</v>
       </c>
       <c r="D25" t="n">
-        <v>1.84</v>
+        <v>2.73</v>
       </c>
       <c r="E25" t="n">
-        <v>26.91</v>
+        <v>168.95</v>
       </c>
       <c r="F25" t="n">
-        <v>26.87</v>
+        <v>161</v>
       </c>
       <c r="G25" t="n">
-        <v>27.57</v>
+        <v>148.48</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.765</v>
+        <v>14.592</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8149999999999999</v>
+        <v>12.429</v>
       </c>
       <c r="J25" t="n">
-        <v>45.91</v>
+        <v>78.28</v>
       </c>
       <c r="K25" t="n">
-        <v>36.36</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>65.03</v>
+        <v>77.31</v>
       </c>
       <c r="M25" t="n">
-        <v>56.82</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>48.73</v>
+        <v>75.59</v>
       </c>
       <c r="O25" t="n">
-        <v>48.21</v>
+        <v>71.27</v>
       </c>
       <c r="P25" t="n">
-        <v>24317.63</v>
+        <v>804.9299999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>18020.48</v>
+        <v>977.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>0.82</v>
       </c>
       <c r="S25" t="n">
-        <v>27.18</v>
+        <v>176.96</v>
       </c>
       <c r="T25" t="n">
-        <v>28.57</v>
+        <v>188.75</v>
       </c>
       <c r="U25" t="n">
-        <v>26.97</v>
+        <v>173.2</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
@@ -2287,69 +2287,69 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2202</v>
+        <v>601899</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.02</v>
+        <v>34.91</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.11</v>
+        <v>0.32</v>
       </c>
       <c r="E26" t="n">
-        <v>24.47</v>
+        <v>34.2</v>
       </c>
       <c r="F26" t="n">
-        <v>24.28</v>
+        <v>33.82</v>
       </c>
       <c r="G26" t="n">
-        <v>26.28</v>
+        <v>33.16</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.965</v>
+        <v>-0.4</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.83</v>
+        <v>-0.791</v>
       </c>
       <c r="J26" t="n">
-        <v>46.94</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>30.58</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>79.68000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="M26" t="n">
-        <v>50.43</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>44.3</v>
+        <v>54.47</v>
       </c>
       <c r="O26" t="n">
-        <v>47</v>
+        <v>50.11</v>
       </c>
       <c r="P26" t="n">
-        <v>25813.14</v>
+        <v>29917.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>23761.5</v>
+        <v>30062.58</v>
       </c>
       <c r="R26" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>25.43</v>
+        <v>35.75</v>
       </c>
       <c r="T26" t="n">
-        <v>25.95</v>
+        <v>36</v>
       </c>
       <c r="U26" t="n">
-        <v>24.84</v>
+        <v>34.81</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
@@ -2360,69 +2360,69 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>301128</v>
+        <v>600219</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>177.86</v>
+        <v>6.2</v>
       </c>
       <c r="D27" t="n">
-        <v>2.73</v>
+        <v>-2.82</v>
       </c>
       <c r="E27" t="n">
-        <v>168.95</v>
+        <v>6.26</v>
       </c>
       <c r="F27" t="n">
-        <v>161</v>
+        <v>6.2</v>
       </c>
       <c r="G27" t="n">
-        <v>148.48</v>
+        <v>6.14</v>
       </c>
       <c r="H27" t="n">
-        <v>14.592</v>
+        <v>-0.129</v>
       </c>
       <c r="I27" t="n">
-        <v>12.429</v>
+        <v>-0.165</v>
       </c>
       <c r="J27" t="n">
-        <v>78.28</v>
+        <v>67.59</v>
       </c>
       <c r="K27" t="n">
-        <v>78.76000000000001</v>
+        <v>60.47</v>
       </c>
       <c r="L27" t="n">
-        <v>77.31</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>80.34999999999999</v>
+        <v>47.71</v>
       </c>
       <c r="N27" t="n">
-        <v>75.59</v>
+        <v>46.18</v>
       </c>
       <c r="O27" t="n">
-        <v>71.27</v>
+        <v>47.58</v>
       </c>
       <c r="P27" t="n">
-        <v>804.9299999999999</v>
+        <v>22466.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>977.16</v>
+        <v>25256.99</v>
       </c>
       <c r="R27" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="S27" t="n">
-        <v>176.96</v>
+        <v>6.38</v>
       </c>
       <c r="T27" t="n">
-        <v>188.75</v>
+        <v>6.4</v>
       </c>
       <c r="U27" t="n">
-        <v>173.2</v>
+        <v>6.18</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
@@ -2433,69 +2433,69 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>601899</v>
+        <v>601939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>34.91</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.32</v>
+        <v>1.07</v>
       </c>
       <c r="E28" t="n">
-        <v>34.2</v>
+        <v>9.33</v>
       </c>
       <c r="F28" t="n">
-        <v>33.82</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>33.16</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4</v>
+        <v>0.074</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.791</v>
+        <v>0.095</v>
       </c>
       <c r="J28" t="n">
-        <v>72.48999999999999</v>
+        <v>48.14</v>
       </c>
       <c r="K28" t="n">
-        <v>68.84999999999999</v>
+        <v>43.34</v>
       </c>
       <c r="L28" t="n">
-        <v>79.75</v>
+        <v>57.73</v>
       </c>
       <c r="M28" t="n">
-        <v>65.23999999999999</v>
+        <v>61.73</v>
       </c>
       <c r="N28" t="n">
-        <v>54.47</v>
+        <v>58.1</v>
       </c>
       <c r="O28" t="n">
-        <v>50.11</v>
+        <v>57.31</v>
       </c>
       <c r="P28" t="n">
-        <v>29917.92</v>
+        <v>9775.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>30062.58</v>
+        <v>9215.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="S28" t="n">
-        <v>35.75</v>
+        <v>9.32</v>
       </c>
       <c r="T28" t="n">
-        <v>36</v>
+        <v>9.52</v>
       </c>
       <c r="U28" t="n">
-        <v>34.81</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
@@ -2506,69 +2506,69 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>600219</v>
+        <v>600048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>保利发展</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.2</v>
+        <v>5.94</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.82</v>
+        <v>-0.17</v>
       </c>
       <c r="E29" t="n">
-        <v>6.26</v>
+        <v>5.76</v>
       </c>
       <c r="F29" t="n">
-        <v>6.2</v>
+        <v>5.71</v>
       </c>
       <c r="G29" t="n">
-        <v>6.14</v>
+        <v>5.86</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.129</v>
+        <v>-0.168</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.165</v>
+        <v>-0.21</v>
       </c>
       <c r="J29" t="n">
-        <v>67.59</v>
+        <v>62.05</v>
       </c>
       <c r="K29" t="n">
-        <v>60.47</v>
+        <v>43.05</v>
       </c>
       <c r="L29" t="n">
-        <v>81.84999999999999</v>
+        <v>100.06</v>
       </c>
       <c r="M29" t="n">
-        <v>47.71</v>
+        <v>63.79</v>
       </c>
       <c r="N29" t="n">
-        <v>46.18</v>
+        <v>50.12</v>
       </c>
       <c r="O29" t="n">
-        <v>47.58</v>
+        <v>45.19</v>
       </c>
       <c r="P29" t="n">
-        <v>22466.7</v>
+        <v>14963.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>25256.99</v>
+        <v>10656.49</v>
       </c>
       <c r="R29" t="n">
-        <v>0.89</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>6.38</v>
+        <v>5.95</v>
       </c>
       <c r="T29" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="U29" t="n">
-        <v>6.18</v>
+        <v>5.86</v>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
@@ -2579,69 +2579,69 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>601939</v>
+        <v>600941</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.460000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>1.07</v>
+        <v>0.17</v>
       </c>
       <c r="E30" t="n">
-        <v>9.33</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>9.359999999999999</v>
+        <v>93.61</v>
       </c>
       <c r="G30" t="n">
-        <v>9.369999999999999</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.074</v>
+        <v>-0.522</v>
       </c>
       <c r="I30" t="n">
-        <v>0.095</v>
+        <v>-0.552</v>
       </c>
       <c r="J30" t="n">
-        <v>48.14</v>
+        <v>60.36</v>
       </c>
       <c r="K30" t="n">
-        <v>43.34</v>
+        <v>55.56</v>
       </c>
       <c r="L30" t="n">
-        <v>57.73</v>
+        <v>69.97</v>
       </c>
       <c r="M30" t="n">
-        <v>61.73</v>
+        <v>47.45</v>
       </c>
       <c r="N30" t="n">
-        <v>58.1</v>
+        <v>44.66</v>
       </c>
       <c r="O30" t="n">
-        <v>57.31</v>
+        <v>44.22</v>
       </c>
       <c r="P30" t="n">
-        <v>9775.32</v>
+        <v>774.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>9215.02</v>
+        <v>849.77</v>
       </c>
       <c r="R30" t="n">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="S30" t="n">
-        <v>9.32</v>
+        <v>93.5</v>
       </c>
       <c r="T30" t="n">
-        <v>9.52</v>
+        <v>93.88</v>
       </c>
       <c r="U30" t="n">
-        <v>9.300000000000001</v>
+        <v>93.41</v>
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
@@ -2652,69 +2652,69 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>600048</v>
+        <v>2352</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>保利发展</t>
+          <t>顺丰控股</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.94</v>
+        <v>37.66</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.17</v>
+        <v>1.29</v>
       </c>
       <c r="E31" t="n">
-        <v>5.76</v>
+        <v>37.34</v>
       </c>
       <c r="F31" t="n">
-        <v>5.71</v>
+        <v>37.63</v>
       </c>
       <c r="G31" t="n">
-        <v>5.86</v>
+        <v>37.14</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.168</v>
+        <v>0.027</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.21</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>62.05</v>
+        <v>44.09</v>
       </c>
       <c r="K31" t="n">
-        <v>43.05</v>
+        <v>47.92</v>
       </c>
       <c r="L31" t="n">
-        <v>100.06</v>
+        <v>36.43</v>
       </c>
       <c r="M31" t="n">
-        <v>63.79</v>
+        <v>57.04</v>
       </c>
       <c r="N31" t="n">
-        <v>50.12</v>
+        <v>53.5</v>
       </c>
       <c r="O31" t="n">
-        <v>45.19</v>
+        <v>50.95</v>
       </c>
       <c r="P31" t="n">
-        <v>14963.01</v>
+        <v>2730.62</v>
       </c>
       <c r="Q31" t="n">
-        <v>10656.49</v>
+        <v>2230.89</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>5.95</v>
+        <v>37.5</v>
       </c>
       <c r="T31" t="n">
-        <v>6.09</v>
+        <v>38.23</v>
       </c>
       <c r="U31" t="n">
-        <v>5.86</v>
+        <v>37.5</v>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
@@ -2725,69 +2725,69 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>600941</v>
+        <v>603803</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.70999999999999</v>
+        <v>15.52</v>
       </c>
       <c r="D32" t="n">
-        <v>0.17</v>
+        <v>3.47</v>
       </c>
       <c r="E32" t="n">
-        <v>93.70999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="F32" t="n">
-        <v>93.61</v>
+        <v>14.13</v>
       </c>
       <c r="G32" t="n">
-        <v>94.20999999999999</v>
+        <v>14.07</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.522</v>
+        <v>0.767</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.552</v>
+        <v>0.694</v>
       </c>
       <c r="J32" t="n">
-        <v>60.36</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>55.56</v>
+        <v>61.35</v>
       </c>
       <c r="L32" t="n">
-        <v>69.97</v>
+        <v>76.25</v>
       </c>
       <c r="M32" t="n">
-        <v>47.45</v>
+        <v>69.56</v>
       </c>
       <c r="N32" t="n">
-        <v>44.66</v>
+        <v>63.98</v>
       </c>
       <c r="O32" t="n">
-        <v>44.22</v>
+        <v>61.57</v>
       </c>
       <c r="P32" t="n">
-        <v>774.24</v>
+        <v>11111.31</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.77</v>
+        <v>9337.91</v>
       </c>
       <c r="R32" t="n">
-        <v>0.91</v>
+        <v>1.19</v>
       </c>
       <c r="S32" t="n">
-        <v>93.5</v>
+        <v>15.21</v>
       </c>
       <c r="T32" t="n">
-        <v>93.88</v>
+        <v>16.15</v>
       </c>
       <c r="U32" t="n">
-        <v>93.41</v>
+        <v>15.21</v>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
@@ -2798,69 +2798,69 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2352</v>
+        <v>2624</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.66</v>
+        <v>19.31</v>
       </c>
       <c r="D33" t="n">
-        <v>1.29</v>
+        <v>-0.46</v>
       </c>
       <c r="E33" t="n">
-        <v>37.34</v>
+        <v>19.67</v>
       </c>
       <c r="F33" t="n">
-        <v>37.63</v>
+        <v>19.63</v>
       </c>
       <c r="G33" t="n">
-        <v>37.14</v>
+        <v>18.8</v>
       </c>
       <c r="H33" t="n">
-        <v>0.027</v>
+        <v>0.1</v>
       </c>
       <c r="I33" t="n">
         <v>-0.008999999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>44.09</v>
+        <v>54.51</v>
       </c>
       <c r="K33" t="n">
-        <v>47.92</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>36.43</v>
+        <v>31.24</v>
       </c>
       <c r="M33" t="n">
-        <v>57.04</v>
+        <v>47.57</v>
       </c>
       <c r="N33" t="n">
-        <v>53.5</v>
+        <v>50.38</v>
       </c>
       <c r="O33" t="n">
-        <v>50.95</v>
+        <v>51.35</v>
       </c>
       <c r="P33" t="n">
-        <v>2730.62</v>
+        <v>6372.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>2230.89</v>
+        <v>5688.72</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>37.5</v>
+        <v>19.47</v>
       </c>
       <c r="T33" t="n">
-        <v>38.23</v>
+        <v>20.08</v>
       </c>
       <c r="U33" t="n">
-        <v>37.5</v>
+        <v>19.19</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
@@ -2871,69 +2871,69 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603803</v>
+        <v>2558</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15.52</v>
+        <v>32.05</v>
       </c>
       <c r="D34" t="n">
-        <v>3.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>14.8</v>
+        <v>32.57</v>
       </c>
       <c r="F34" t="n">
-        <v>14.13</v>
+        <v>33.23</v>
       </c>
       <c r="G34" t="n">
-        <v>14.07</v>
+        <v>32.71</v>
       </c>
       <c r="H34" t="n">
-        <v>0.767</v>
+        <v>-1.079</v>
       </c>
       <c r="I34" t="n">
-        <v>0.694</v>
+        <v>-1.28</v>
       </c>
       <c r="J34" t="n">
-        <v>66.31999999999999</v>
+        <v>31.47</v>
       </c>
       <c r="K34" t="n">
-        <v>61.35</v>
+        <v>42.7</v>
       </c>
       <c r="L34" t="n">
-        <v>76.25</v>
+        <v>9.01</v>
       </c>
       <c r="M34" t="n">
-        <v>69.56</v>
+        <v>43.43</v>
       </c>
       <c r="N34" t="n">
-        <v>63.98</v>
+        <v>43.09</v>
       </c>
       <c r="O34" t="n">
-        <v>61.57</v>
+        <v>41.34</v>
       </c>
       <c r="P34" t="n">
-        <v>11111.31</v>
+        <v>6242.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>9337.91</v>
+        <v>5043.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>15.21</v>
+        <v>31.88</v>
       </c>
       <c r="T34" t="n">
-        <v>16.15</v>
+        <v>33.08</v>
       </c>
       <c r="U34" t="n">
-        <v>15.21</v>
+        <v>31.8</v>
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
@@ -2944,69 +2944,69 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2624</v>
+        <v>601088</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>完美世界</t>
+          <t>中国神华</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19.31</v>
+        <v>45.83</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.46</v>
+        <v>0.37</v>
       </c>
       <c r="E35" t="n">
-        <v>19.67</v>
+        <v>46.2</v>
       </c>
       <c r="F35" t="n">
-        <v>19.63</v>
+        <v>46.8</v>
       </c>
       <c r="G35" t="n">
-        <v>18.8</v>
+        <v>47.48</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1</v>
+        <v>0.064</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.472</v>
       </c>
       <c r="J35" t="n">
-        <v>54.51</v>
+        <v>22.18</v>
       </c>
       <c r="K35" t="n">
-        <v>66.15000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="L35" t="n">
-        <v>31.24</v>
+        <v>9.74</v>
       </c>
       <c r="M35" t="n">
-        <v>47.57</v>
+        <v>32.63</v>
       </c>
       <c r="N35" t="n">
-        <v>50.38</v>
+        <v>42.9</v>
       </c>
       <c r="O35" t="n">
-        <v>51.35</v>
+        <v>50.35</v>
       </c>
       <c r="P35" t="n">
-        <v>6372.64</v>
+        <v>2820.62</v>
       </c>
       <c r="Q35" t="n">
-        <v>5688.72</v>
+        <v>3644.53</v>
       </c>
       <c r="R35" t="n">
-        <v>1.12</v>
+        <v>0.77</v>
       </c>
       <c r="S35" t="n">
-        <v>19.47</v>
+        <v>45.21</v>
       </c>
       <c r="T35" t="n">
-        <v>20.08</v>
+        <v>46.01</v>
       </c>
       <c r="U35" t="n">
-        <v>19.19</v>
+        <v>45</v>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
@@ -3017,69 +3017,69 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2558</v>
+        <v>600963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>岳阳林纸</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32.05</v>
+        <v>4.75</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.21</v>
       </c>
       <c r="E36" t="n">
-        <v>32.57</v>
+        <v>4.81</v>
       </c>
       <c r="F36" t="n">
-        <v>33.23</v>
+        <v>4.79</v>
       </c>
       <c r="G36" t="n">
-        <v>32.71</v>
+        <v>4.81</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.079</v>
+        <v>-0.171</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.28</v>
+        <v>-0.196</v>
       </c>
       <c r="J36" t="n">
-        <v>31.47</v>
+        <v>51.08</v>
       </c>
       <c r="K36" t="n">
-        <v>42.7</v>
+        <v>53.76</v>
       </c>
       <c r="L36" t="n">
-        <v>9.01</v>
+        <v>45.73</v>
       </c>
       <c r="M36" t="n">
-        <v>43.43</v>
+        <v>41.16</v>
       </c>
       <c r="N36" t="n">
-        <v>43.09</v>
+        <v>40.21</v>
       </c>
       <c r="O36" t="n">
-        <v>41.34</v>
+        <v>43.42</v>
       </c>
       <c r="P36" t="n">
-        <v>6242.56</v>
+        <v>1946.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>5043.44</v>
+        <v>2916.73</v>
       </c>
       <c r="R36" t="n">
-        <v>1.24</v>
+        <v>0.67</v>
       </c>
       <c r="S36" t="n">
-        <v>31.88</v>
+        <v>4.78</v>
       </c>
       <c r="T36" t="n">
-        <v>33.08</v>
+        <v>4.8</v>
       </c>
       <c r="U36" t="n">
-        <v>31.8</v>
+        <v>4.71</v>
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
@@ -3090,69 +3090,69 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>601088</v>
+        <v>601877</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>45.83</v>
+        <v>34.34</v>
       </c>
       <c r="D37" t="n">
-        <v>0.37</v>
+        <v>2.45</v>
       </c>
       <c r="E37" t="n">
-        <v>46.2</v>
+        <v>33.47</v>
       </c>
       <c r="F37" t="n">
-        <v>46.8</v>
+        <v>32.73</v>
       </c>
       <c r="G37" t="n">
-        <v>47.48</v>
+        <v>33.57</v>
       </c>
       <c r="H37" t="n">
-        <v>0.064</v>
+        <v>-0.224</v>
       </c>
       <c r="I37" t="n">
-        <v>0.472</v>
+        <v>-0.252</v>
       </c>
       <c r="J37" t="n">
-        <v>22.18</v>
+        <v>75.84</v>
       </c>
       <c r="K37" t="n">
-        <v>28.4</v>
+        <v>57.04</v>
       </c>
       <c r="L37" t="n">
-        <v>9.74</v>
+        <v>113.44</v>
       </c>
       <c r="M37" t="n">
-        <v>32.63</v>
+        <v>66.94</v>
       </c>
       <c r="N37" t="n">
-        <v>42.9</v>
+        <v>55.09</v>
       </c>
       <c r="O37" t="n">
-        <v>50.35</v>
+        <v>53.62</v>
       </c>
       <c r="P37" t="n">
-        <v>2820.62</v>
+        <v>4629.95</v>
       </c>
       <c r="Q37" t="n">
-        <v>3644.53</v>
+        <v>3614.17</v>
       </c>
       <c r="R37" t="n">
-        <v>0.77</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>45.21</v>
+        <v>33.8</v>
       </c>
       <c r="T37" t="n">
-        <v>46.01</v>
+        <v>34.55</v>
       </c>
       <c r="U37" t="n">
-        <v>45</v>
+        <v>33.3</v>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
@@ -3163,69 +3163,69 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>600963</v>
+        <v>2049</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>岳阳林纸</t>
+          <t>紫光国微</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.75</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.21</v>
+        <v>-1.21</v>
       </c>
       <c r="E38" t="n">
-        <v>4.81</v>
+        <v>69.87</v>
       </c>
       <c r="F38" t="n">
-        <v>4.79</v>
+        <v>68.22</v>
       </c>
       <c r="G38" t="n">
-        <v>4.81</v>
+        <v>68.59</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.171</v>
+        <v>-1.226</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.196</v>
+        <v>-1.996</v>
       </c>
       <c r="J38" t="n">
-        <v>51.08</v>
+        <v>80.36</v>
       </c>
       <c r="K38" t="n">
-        <v>53.76</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>45.73</v>
+        <v>102.88</v>
       </c>
       <c r="M38" t="n">
-        <v>41.16</v>
+        <v>59.83</v>
       </c>
       <c r="N38" t="n">
-        <v>40.21</v>
+        <v>50.75</v>
       </c>
       <c r="O38" t="n">
-        <v>43.42</v>
+        <v>46.36</v>
       </c>
       <c r="P38" t="n">
-        <v>1946.8</v>
+        <v>1481.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>2916.73</v>
+        <v>1283.51</v>
       </c>
       <c r="R38" t="n">
-        <v>0.67</v>
+        <v>1.15</v>
       </c>
       <c r="S38" t="n">
-        <v>4.78</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>4.8</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="U38" t="n">
-        <v>4.71</v>
+        <v>70.08</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
@@ -3236,69 +3236,69 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>601877</v>
+        <v>601689</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34.34</v>
+        <v>59.12</v>
       </c>
       <c r="D39" t="n">
-        <v>2.45</v>
+        <v>-1.53</v>
       </c>
       <c r="E39" t="n">
-        <v>33.47</v>
+        <v>59.48</v>
       </c>
       <c r="F39" t="n">
-        <v>32.73</v>
+        <v>58.82</v>
       </c>
       <c r="G39" t="n">
-        <v>33.57</v>
+        <v>58.49</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.224</v>
+        <v>-1.366</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.252</v>
+        <v>-2.014</v>
       </c>
       <c r="J39" t="n">
-        <v>75.84</v>
+        <v>63.04</v>
       </c>
       <c r="K39" t="n">
-        <v>57.04</v>
+        <v>59.9</v>
       </c>
       <c r="L39" t="n">
-        <v>113.44</v>
+        <v>69.33</v>
       </c>
       <c r="M39" t="n">
-        <v>66.94</v>
+        <v>50.47</v>
       </c>
       <c r="N39" t="n">
-        <v>55.09</v>
+        <v>46.09</v>
       </c>
       <c r="O39" t="n">
-        <v>53.62</v>
+        <v>42.31</v>
       </c>
       <c r="P39" t="n">
-        <v>4629.95</v>
+        <v>2676.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>3614.17</v>
+        <v>2522.56</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="S39" t="n">
-        <v>33.8</v>
+        <v>60.67</v>
       </c>
       <c r="T39" t="n">
-        <v>34.55</v>
+        <v>60.76</v>
       </c>
       <c r="U39" t="n">
-        <v>33.3</v>
+        <v>58.74</v>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
@@ -3309,69 +3309,69 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>紫光国微</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>70.18000000000001</v>
+        <v>45.11</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.21</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>69.87</v>
+        <v>44.75</v>
       </c>
       <c r="F40" t="n">
-        <v>68.22</v>
+        <v>43.81</v>
       </c>
       <c r="G40" t="n">
-        <v>68.59</v>
+        <v>43.78</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.226</v>
+        <v>-0.787</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.996</v>
+        <v>-1.312</v>
       </c>
       <c r="J40" t="n">
-        <v>80.36</v>
+        <v>74.12</v>
       </c>
       <c r="K40" t="n">
-        <v>69.09999999999999</v>
+        <v>65.81</v>
       </c>
       <c r="L40" t="n">
-        <v>102.88</v>
+        <v>90.73</v>
       </c>
       <c r="M40" t="n">
-        <v>59.83</v>
+        <v>60.48</v>
       </c>
       <c r="N40" t="n">
-        <v>50.75</v>
+        <v>51.6</v>
       </c>
       <c r="O40" t="n">
-        <v>46.36</v>
+        <v>46.92</v>
       </c>
       <c r="P40" t="n">
-        <v>1481.07</v>
+        <v>9233.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>1283.51</v>
+        <v>7404.58</v>
       </c>
       <c r="R40" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>71.40000000000001</v>
+        <v>46.18</v>
       </c>
       <c r="T40" t="n">
-        <v>71.56999999999999</v>
+        <v>46.48</v>
       </c>
       <c r="U40" t="n">
-        <v>70.08</v>
+        <v>44.82</v>
       </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
@@ -3382,69 +3382,69 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>688271</v>
+        <v>887</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>联影医疗</t>
+          <t>中鼎股份</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>114</v>
+        <v>18.6</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.61</v>
+        <v>-1.17</v>
       </c>
       <c r="E41" t="n">
-        <v>113.69</v>
+        <v>18.59</v>
       </c>
       <c r="F41" t="n">
-        <v>113.47</v>
+        <v>18.26</v>
       </c>
       <c r="G41" t="n">
-        <v>113.57</v>
+        <v>18.21</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.111</v>
+        <v>-0.329</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.768</v>
+        <v>-0.526</v>
       </c>
       <c r="J41" t="n">
-        <v>71.04000000000001</v>
+        <v>77.78</v>
       </c>
       <c r="K41" t="n">
-        <v>64.70999999999999</v>
+        <v>70.84</v>
       </c>
       <c r="L41" t="n">
-        <v>83.69</v>
+        <v>91.67</v>
       </c>
       <c r="M41" t="n">
-        <v>51.31</v>
+        <v>56.53</v>
       </c>
       <c r="N41" t="n">
-        <v>46.39</v>
+        <v>49.35</v>
       </c>
       <c r="O41" t="n">
-        <v>43.35</v>
+        <v>43.99</v>
       </c>
       <c r="P41" t="n">
-        <v>436.12</v>
+        <v>1574.51</v>
       </c>
       <c r="Q41" t="n">
-        <v>389.89</v>
+        <v>1617.22</v>
       </c>
       <c r="R41" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="S41" t="n">
-        <v>115.82</v>
+        <v>18.89</v>
       </c>
       <c r="T41" t="n">
-        <v>116.1</v>
+        <v>19.03</v>
       </c>
       <c r="U41" t="n">
-        <v>113.86</v>
+        <v>18.6</v>
       </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
@@ -3455,69 +3455,69 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>688608</v>
+        <v>603236</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>恒玄科技</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>168.08</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.18</v>
+        <v>-1.55</v>
       </c>
       <c r="E42" t="n">
-        <v>168.18</v>
+        <v>76.78</v>
       </c>
       <c r="F42" t="n">
-        <v>167.65</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>167.16</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>-5.375</v>
+        <v>-1.217</v>
       </c>
       <c r="I42" t="n">
-        <v>-7.273</v>
+        <v>-2.113</v>
       </c>
       <c r="J42" t="n">
-        <v>42.28</v>
+        <v>74.67</v>
       </c>
       <c r="K42" t="n">
-        <v>41.65</v>
+        <v>69.3</v>
       </c>
       <c r="L42" t="n">
-        <v>43.52</v>
+        <v>85.41</v>
       </c>
       <c r="M42" t="n">
-        <v>49.34</v>
+        <v>55.95</v>
       </c>
       <c r="N42" t="n">
-        <v>44.86</v>
+        <v>50.2</v>
       </c>
       <c r="O42" t="n">
-        <v>41.57</v>
+        <v>44.51</v>
       </c>
       <c r="P42" t="n">
-        <v>452.91</v>
+        <v>504.52</v>
       </c>
       <c r="Q42" t="n">
-        <v>352.7</v>
+        <v>508.32</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="S42" t="n">
-        <v>171.74</v>
+        <v>78.28</v>
       </c>
       <c r="T42" t="n">
-        <v>174.24</v>
+        <v>78.88</v>
       </c>
       <c r="U42" t="n">
-        <v>167.81</v>
+        <v>76.25</v>
       </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
@@ -3528,69 +3528,69 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>688099</v>
+        <v>603072</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>晶晨股份</t>
+          <t>天和磁材</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>81.17</v>
+        <v>37.04</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.45</v>
+        <v>-0.35</v>
       </c>
       <c r="E43" t="n">
-        <v>82.09999999999999</v>
+        <v>36.91</v>
       </c>
       <c r="F43" t="n">
-        <v>80.08</v>
+        <v>36.43</v>
       </c>
       <c r="G43" t="n">
-        <v>81.59999999999999</v>
+        <v>36.35</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.52</v>
+        <v>-0.855</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.066</v>
+        <v>-1.224</v>
       </c>
       <c r="J43" t="n">
-        <v>63.83</v>
+        <v>73.17</v>
       </c>
       <c r="K43" t="n">
-        <v>56.6</v>
+        <v>69.33</v>
       </c>
       <c r="L43" t="n">
-        <v>78.29000000000001</v>
+        <v>80.86</v>
       </c>
       <c r="M43" t="n">
-        <v>48.8</v>
+        <v>58.92</v>
       </c>
       <c r="N43" t="n">
-        <v>46.59</v>
+        <v>47.3</v>
       </c>
       <c r="O43" t="n">
-        <v>46.22</v>
+        <v>43.79</v>
       </c>
       <c r="P43" t="n">
-        <v>902.5599999999999</v>
+        <v>220.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>937.78</v>
+        <v>226.31</v>
       </c>
       <c r="R43" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="S43" t="n">
-        <v>83.72</v>
+        <v>37.15</v>
       </c>
       <c r="T43" t="n">
-        <v>84.2</v>
+        <v>37.57</v>
       </c>
       <c r="U43" t="n">
-        <v>80.8</v>
+        <v>36.96</v>
       </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
@@ -3601,69 +3601,69 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>688332</v>
+        <v>301023</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>126.31</v>
+        <v>40.19</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>125.63</v>
+        <v>39.98</v>
       </c>
       <c r="F44" t="n">
-        <v>123.8</v>
+        <v>39.26</v>
       </c>
       <c r="G44" t="n">
-        <v>120.44</v>
+        <v>39.42</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.274</v>
+        <v>-0.872</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.786</v>
+        <v>-1.268</v>
       </c>
       <c r="J44" t="n">
-        <v>66.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>69.40000000000001</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>61.89</v>
+        <v>98.69</v>
       </c>
       <c r="M44" t="n">
-        <v>63.67</v>
+        <v>58.94</v>
       </c>
       <c r="N44" t="n">
-        <v>55.75</v>
+        <v>49.02</v>
       </c>
       <c r="O44" t="n">
-        <v>49.78</v>
+        <v>46.61</v>
       </c>
       <c r="P44" t="n">
-        <v>213.58</v>
+        <v>125.04</v>
       </c>
       <c r="Q44" t="n">
-        <v>174.33</v>
+        <v>123.45</v>
       </c>
       <c r="R44" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="S44" t="n">
-        <v>128</v>
+        <v>40.25</v>
       </c>
       <c r="T44" t="n">
-        <v>129.27</v>
+        <v>40.88</v>
       </c>
       <c r="U44" t="n">
-        <v>126</v>
+        <v>40.05</v>
       </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
@@ -3674,69 +3674,69 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>688049</v>
+        <v>2074</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>46.65</v>
+        <v>38.72</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.25</v>
+        <v>-3.01</v>
       </c>
       <c r="E45" t="n">
-        <v>46.49</v>
+        <v>38.45</v>
       </c>
       <c r="F45" t="n">
-        <v>45.59</v>
+        <v>36.54</v>
       </c>
       <c r="G45" t="n">
-        <v>45.56</v>
+        <v>36.78</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.922</v>
+        <v>0.198</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.461</v>
+        <v>-0.279</v>
       </c>
       <c r="J45" t="n">
-        <v>73.20999999999999</v>
+        <v>78.92</v>
       </c>
       <c r="K45" t="n">
-        <v>64.95</v>
+        <v>63.62</v>
       </c>
       <c r="L45" t="n">
-        <v>89.73999999999999</v>
+        <v>109.54</v>
       </c>
       <c r="M45" t="n">
-        <v>56.88</v>
+        <v>62.67</v>
       </c>
       <c r="N45" t="n">
-        <v>49.59</v>
+        <v>58.33</v>
       </c>
       <c r="O45" t="n">
-        <v>45.76</v>
+        <v>54.12</v>
       </c>
       <c r="P45" t="n">
-        <v>493.2</v>
+        <v>7011.44</v>
       </c>
       <c r="Q45" t="n">
-        <v>454.53</v>
+        <v>5068.11</v>
       </c>
       <c r="R45" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>47.43</v>
+        <v>39.65</v>
       </c>
       <c r="T45" t="n">
-        <v>47.95</v>
+        <v>39.65</v>
       </c>
       <c r="U45" t="n">
-        <v>46.56</v>
+        <v>38.6</v>
       </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
@@ -3747,69 +3747,69 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>601689</v>
+        <v>300450</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>59.12</v>
+        <v>52.86</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.53</v>
+        <v>-2.44</v>
       </c>
       <c r="E46" t="n">
-        <v>59.48</v>
+        <v>52.57</v>
       </c>
       <c r="F46" t="n">
-        <v>58.82</v>
+        <v>50.32</v>
       </c>
       <c r="G46" t="n">
-        <v>58.49</v>
+        <v>49.38</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.366</v>
+        <v>0.253</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.014</v>
+        <v>-0.598</v>
       </c>
       <c r="J46" t="n">
-        <v>63.04</v>
+        <v>83.53</v>
       </c>
       <c r="K46" t="n">
-        <v>59.9</v>
+        <v>76.19</v>
       </c>
       <c r="L46" t="n">
-        <v>69.33</v>
+        <v>98.22</v>
       </c>
       <c r="M46" t="n">
-        <v>50.47</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>46.09</v>
+        <v>58.6</v>
       </c>
       <c r="O46" t="n">
-        <v>42.31</v>
+        <v>53.12</v>
       </c>
       <c r="P46" t="n">
-        <v>2676.6</v>
+        <v>5435.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>2522.56</v>
+        <v>4796.98</v>
       </c>
       <c r="R46" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="S46" t="n">
-        <v>60.67</v>
+        <v>54.6</v>
       </c>
       <c r="T46" t="n">
-        <v>60.76</v>
+        <v>54.75</v>
       </c>
       <c r="U46" t="n">
-        <v>58.74</v>
+        <v>52.6</v>
       </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
@@ -3820,69 +3820,69 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2050</v>
+        <v>603200</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>45.11</v>
+        <v>61.86</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.58</v>
       </c>
       <c r="E47" t="n">
-        <v>44.75</v>
+        <v>61.09</v>
       </c>
       <c r="F47" t="n">
-        <v>43.81</v>
+        <v>59.19</v>
       </c>
       <c r="G47" t="n">
-        <v>43.78</v>
+        <v>59.12</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.787</v>
+        <v>-2.274</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.312</v>
+        <v>-3.551</v>
       </c>
       <c r="J47" t="n">
-        <v>74.12</v>
+        <v>70.67</v>
       </c>
       <c r="K47" t="n">
-        <v>65.81</v>
+        <v>59.28</v>
       </c>
       <c r="L47" t="n">
-        <v>90.73</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>60.48</v>
+        <v>58.91</v>
       </c>
       <c r="N47" t="n">
-        <v>51.6</v>
+        <v>49.66</v>
       </c>
       <c r="O47" t="n">
-        <v>46.92</v>
+        <v>43.82</v>
       </c>
       <c r="P47" t="n">
-        <v>9233.34</v>
+        <v>1166.97</v>
       </c>
       <c r="Q47" t="n">
-        <v>7404.58</v>
+        <v>689.59</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="S47" t="n">
-        <v>46.18</v>
+        <v>63</v>
       </c>
       <c r="T47" t="n">
-        <v>46.48</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="U47" t="n">
-        <v>44.82</v>
+        <v>61.5</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
@@ -3893,69 +3893,69 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>887</v>
+        <v>300409</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>道氏技术</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>18.6</v>
+        <v>26.52</v>
       </c>
       <c r="D48" t="n">
-        <v>-1.17</v>
+        <v>-6.02</v>
       </c>
       <c r="E48" t="n">
-        <v>18.59</v>
+        <v>26.79</v>
       </c>
       <c r="F48" t="n">
-        <v>18.26</v>
+        <v>25.77</v>
       </c>
       <c r="G48" t="n">
-        <v>18.21</v>
+        <v>25.52</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.329</v>
+        <v>-0.243</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.526</v>
+        <v>-0.636</v>
       </c>
       <c r="J48" t="n">
-        <v>77.78</v>
+        <v>76.42</v>
       </c>
       <c r="K48" t="n">
-        <v>70.84</v>
+        <v>70.91</v>
       </c>
       <c r="L48" t="n">
-        <v>91.67</v>
+        <v>87.44</v>
       </c>
       <c r="M48" t="n">
-        <v>56.53</v>
+        <v>53.76</v>
       </c>
       <c r="N48" t="n">
-        <v>49.35</v>
+        <v>51.22</v>
       </c>
       <c r="O48" t="n">
-        <v>43.99</v>
+        <v>49.31</v>
       </c>
       <c r="P48" t="n">
-        <v>1574.51</v>
+        <v>5912.58</v>
       </c>
       <c r="Q48" t="n">
-        <v>1617.22</v>
+        <v>3027.44</v>
       </c>
       <c r="R48" t="n">
-        <v>0.97</v>
+        <v>1.95</v>
       </c>
       <c r="S48" t="n">
-        <v>18.89</v>
+        <v>27.3</v>
       </c>
       <c r="T48" t="n">
-        <v>19.03</v>
+        <v>27.49</v>
       </c>
       <c r="U48" t="n">
-        <v>18.6</v>
+        <v>26.41</v>
       </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
@@ -3966,69 +3966,69 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>603236</v>
+        <v>2202</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>76.73999999999999</v>
+        <v>25.02</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.55</v>
+        <v>-1.11</v>
       </c>
       <c r="E49" t="n">
-        <v>76.78</v>
+        <v>24.47</v>
       </c>
       <c r="F49" t="n">
-        <v>75.34999999999999</v>
+        <v>24.28</v>
       </c>
       <c r="G49" t="n">
-        <v>74.95999999999999</v>
+        <v>26.28</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.217</v>
+        <v>-0.965</v>
       </c>
       <c r="I49" t="n">
-        <v>-2.113</v>
+        <v>-0.83</v>
       </c>
       <c r="J49" t="n">
-        <v>74.67</v>
+        <v>46.94</v>
       </c>
       <c r="K49" t="n">
-        <v>69.3</v>
+        <v>30.58</v>
       </c>
       <c r="L49" t="n">
-        <v>85.41</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>55.95</v>
+        <v>50.43</v>
       </c>
       <c r="N49" t="n">
-        <v>50.2</v>
+        <v>44.3</v>
       </c>
       <c r="O49" t="n">
-        <v>44.51</v>
+        <v>47</v>
       </c>
       <c r="P49" t="n">
-        <v>504.52</v>
+        <v>25813.14</v>
       </c>
       <c r="Q49" t="n">
-        <v>508.32</v>
+        <v>23761.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="S49" t="n">
-        <v>78.28</v>
+        <v>25.43</v>
       </c>
       <c r="T49" t="n">
-        <v>78.88</v>
+        <v>25.95</v>
       </c>
       <c r="U49" t="n">
-        <v>76.25</v>
+        <v>24.84</v>
       </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
@@ -4039,69 +4039,69 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>603072</v>
+        <v>600990</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>天和磁材</t>
+          <t>四创电子</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37.04</v>
+        <v>23.75</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.35</v>
+        <v>-0.71</v>
       </c>
       <c r="E50" t="n">
-        <v>36.91</v>
+        <v>23.52</v>
       </c>
       <c r="F50" t="n">
-        <v>36.43</v>
+        <v>22.87</v>
       </c>
       <c r="G50" t="n">
-        <v>36.35</v>
+        <v>22.94</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.855</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.224</v>
+        <v>-0.902</v>
       </c>
       <c r="J50" t="n">
-        <v>73.17</v>
+        <v>79.16</v>
       </c>
       <c r="K50" t="n">
-        <v>69.33</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>80.86</v>
+        <v>106.84</v>
       </c>
       <c r="M50" t="n">
-        <v>58.92</v>
+        <v>65.42</v>
       </c>
       <c r="N50" t="n">
-        <v>47.3</v>
+        <v>51.67</v>
       </c>
       <c r="O50" t="n">
-        <v>43.79</v>
+        <v>44.29</v>
       </c>
       <c r="P50" t="n">
-        <v>220.58</v>
+        <v>437.33</v>
       </c>
       <c r="Q50" t="n">
-        <v>226.31</v>
+        <v>448.34</v>
       </c>
       <c r="R50" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="S50" t="n">
-        <v>37.15</v>
+        <v>24</v>
       </c>
       <c r="T50" t="n">
-        <v>37.57</v>
+        <v>24.18</v>
       </c>
       <c r="U50" t="n">
-        <v>36.96</v>
+        <v>23.64</v>
       </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
@@ -4112,69 +4112,69 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>301023</v>
+        <v>2025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>奕帆传动</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>40.19</v>
+        <v>79.67</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="E51" t="n">
-        <v>39.98</v>
+        <v>78.03</v>
       </c>
       <c r="F51" t="n">
-        <v>39.26</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>39.42</v>
+        <v>67.45</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.872</v>
+        <v>5.583</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.268</v>
+        <v>4.24</v>
       </c>
       <c r="J51" t="n">
-        <v>77.90000000000001</v>
+        <v>85.11</v>
       </c>
       <c r="K51" t="n">
-        <v>67.51000000000001</v>
+        <v>80</v>
       </c>
       <c r="L51" t="n">
-        <v>98.69</v>
+        <v>95.34</v>
       </c>
       <c r="M51" t="n">
-        <v>58.94</v>
+        <v>77.31</v>
       </c>
       <c r="N51" t="n">
-        <v>49.02</v>
+        <v>71.17</v>
       </c>
       <c r="O51" t="n">
-        <v>46.61</v>
+        <v>66.45</v>
       </c>
       <c r="P51" t="n">
-        <v>125.04</v>
+        <v>4082.85</v>
       </c>
       <c r="Q51" t="n">
-        <v>123.45</v>
+        <v>3578.62</v>
       </c>
       <c r="R51" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="S51" t="n">
-        <v>40.25</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="T51" t="n">
-        <v>40.88</v>
+        <v>82.58</v>
       </c>
       <c r="U51" t="n">
-        <v>40.05</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
@@ -4185,69 +4185,69 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2074</v>
+        <v>600584</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38.72</v>
+        <v>43.59</v>
       </c>
       <c r="D52" t="n">
-        <v>-3.01</v>
+        <v>-1.69</v>
       </c>
       <c r="E52" t="n">
-        <v>38.45</v>
+        <v>43.14</v>
       </c>
       <c r="F52" t="n">
-        <v>36.54</v>
+        <v>41.28</v>
       </c>
       <c r="G52" t="n">
-        <v>36.78</v>
+        <v>41.07</v>
       </c>
       <c r="H52" t="n">
-        <v>0.198</v>
+        <v>-0.345</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.279</v>
+        <v>-1.024</v>
       </c>
       <c r="J52" t="n">
-        <v>78.92</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>63.62</v>
+        <v>68.14</v>
       </c>
       <c r="L52" t="n">
-        <v>109.54</v>
+        <v>99.67</v>
       </c>
       <c r="M52" t="n">
-        <v>62.67</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>58.33</v>
+        <v>56.23</v>
       </c>
       <c r="O52" t="n">
-        <v>54.12</v>
+        <v>51.75</v>
       </c>
       <c r="P52" t="n">
-        <v>7011.44</v>
+        <v>6806.66</v>
       </c>
       <c r="Q52" t="n">
-        <v>5068.11</v>
+        <v>5197.98</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S52" t="n">
-        <v>39.65</v>
+        <v>44.5</v>
       </c>
       <c r="T52" t="n">
-        <v>39.65</v>
+        <v>44.7</v>
       </c>
       <c r="U52" t="n">
-        <v>38.6</v>
+        <v>43.36</v>
       </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
@@ -4258,69 +4258,69 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>300450</v>
+        <v>300759</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52.86</v>
+        <v>31.3</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.44</v>
+        <v>-0.25</v>
       </c>
       <c r="E53" t="n">
-        <v>52.57</v>
+        <v>31</v>
       </c>
       <c r="F53" t="n">
-        <v>50.32</v>
+        <v>30.66</v>
       </c>
       <c r="G53" t="n">
-        <v>49.38</v>
+        <v>28.56</v>
       </c>
       <c r="H53" t="n">
-        <v>0.253</v>
+        <v>0.859</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.598</v>
+        <v>0.459</v>
       </c>
       <c r="J53" t="n">
-        <v>83.53</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>76.19</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>98.22</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>64.04000000000001</v>
+        <v>73.56</v>
       </c>
       <c r="N53" t="n">
-        <v>58.6</v>
+        <v>67.19</v>
       </c>
       <c r="O53" t="n">
-        <v>53.12</v>
+        <v>59.78</v>
       </c>
       <c r="P53" t="n">
-        <v>5435.7</v>
+        <v>4922.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>4796.98</v>
+        <v>3616.74</v>
       </c>
       <c r="R53" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="S53" t="n">
-        <v>54.6</v>
+        <v>31.98</v>
       </c>
       <c r="T53" t="n">
-        <v>54.75</v>
+        <v>32.09</v>
       </c>
       <c r="U53" t="n">
-        <v>52.6</v>
+        <v>30.61</v>
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
@@ -4331,69 +4331,69 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>688778</v>
+        <v>301333</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>诺思格</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>75.8</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>0.49</v>
+        <v>1.15</v>
       </c>
       <c r="E54" t="n">
-        <v>74.64</v>
+        <v>67.84</v>
       </c>
       <c r="F54" t="n">
-        <v>72.98</v>
+        <v>67.98</v>
       </c>
       <c r="G54" t="n">
-        <v>72.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.83</v>
+        <v>0.582</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.639</v>
+        <v>-0.147</v>
       </c>
       <c r="J54" t="n">
-        <v>67.78</v>
+        <v>62.34</v>
       </c>
       <c r="K54" t="n">
-        <v>60.05</v>
+        <v>58.19</v>
       </c>
       <c r="L54" t="n">
-        <v>83.23999999999999</v>
+        <v>70.64</v>
       </c>
       <c r="M54" t="n">
-        <v>61.04</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>53.65</v>
+        <v>57.9</v>
       </c>
       <c r="O54" t="n">
-        <v>49.5</v>
+        <v>53.51</v>
       </c>
       <c r="P54" t="n">
-        <v>882.53</v>
+        <v>259.39</v>
       </c>
       <c r="Q54" t="n">
-        <v>540.36</v>
+        <v>261.46</v>
       </c>
       <c r="R54" t="n">
-        <v>1.63</v>
+        <v>0.99</v>
       </c>
       <c r="S54" t="n">
-        <v>76</v>
+        <v>69.37</v>
       </c>
       <c r="T54" t="n">
-        <v>77.97</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="U54" t="n">
-        <v>74.76000000000001</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
@@ -4404,69 +4404,69 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>688116</v>
+        <v>963</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>天奈科技</t>
+          <t>华东医药</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>40.33</v>
+        <v>35.67</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.25</v>
+        <v>1.91</v>
       </c>
       <c r="E55" t="n">
-        <v>40.22</v>
+        <v>35.52</v>
       </c>
       <c r="F55" t="n">
-        <v>39.35</v>
+        <v>35.93</v>
       </c>
       <c r="G55" t="n">
-        <v>40.06</v>
+        <v>35.37</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.919</v>
+        <v>0.018</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.282</v>
+        <v>-0.001</v>
       </c>
       <c r="J55" t="n">
-        <v>71.28</v>
+        <v>39.54</v>
       </c>
       <c r="K55" t="n">
-        <v>59.14</v>
+        <v>48.21</v>
       </c>
       <c r="L55" t="n">
-        <v>95.55</v>
+        <v>22.2</v>
       </c>
       <c r="M55" t="n">
-        <v>53.43</v>
+        <v>51.77</v>
       </c>
       <c r="N55" t="n">
-        <v>47.78</v>
+        <v>51.17</v>
       </c>
       <c r="O55" t="n">
-        <v>44.41</v>
+        <v>48.9</v>
       </c>
       <c r="P55" t="n">
-        <v>713.34</v>
+        <v>1575.56</v>
       </c>
       <c r="Q55" t="n">
-        <v>730.76</v>
+        <v>1158.39</v>
       </c>
       <c r="R55" t="n">
-        <v>0.98</v>
+        <v>1.36</v>
       </c>
       <c r="S55" t="n">
-        <v>41.49</v>
+        <v>35.78</v>
       </c>
       <c r="T55" t="n">
-        <v>41.79</v>
+        <v>35.93</v>
       </c>
       <c r="U55" t="n">
-        <v>40.15</v>
+        <v>35.3</v>
       </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
@@ -4477,69 +4477,69 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>603200</v>
+        <v>603658</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>安图生物</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>61.86</v>
+        <v>34.42</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.58</v>
+        <v>0.73</v>
       </c>
       <c r="E56" t="n">
-        <v>61.09</v>
+        <v>34.27</v>
       </c>
       <c r="F56" t="n">
-        <v>59.19</v>
+        <v>34.37</v>
       </c>
       <c r="G56" t="n">
-        <v>59.12</v>
+        <v>33.98</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.274</v>
+        <v>-0.182</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.551</v>
+        <v>-0.309</v>
       </c>
       <c r="J56" t="n">
-        <v>70.67</v>
+        <v>54.57</v>
       </c>
       <c r="K56" t="n">
-        <v>59.28</v>
+        <v>61.04</v>
       </c>
       <c r="L56" t="n">
-        <v>93.43000000000001</v>
+        <v>41.62</v>
       </c>
       <c r="M56" t="n">
-        <v>58.91</v>
+        <v>54.65</v>
       </c>
       <c r="N56" t="n">
-        <v>49.66</v>
+        <v>50.79</v>
       </c>
       <c r="O56" t="n">
-        <v>43.82</v>
+        <v>47.34</v>
       </c>
       <c r="P56" t="n">
-        <v>1166.97</v>
+        <v>161.83</v>
       </c>
       <c r="Q56" t="n">
-        <v>689.59</v>
+        <v>198.64</v>
       </c>
       <c r="R56" t="n">
-        <v>1.69</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S56" t="n">
-        <v>63</v>
+        <v>34.33</v>
       </c>
       <c r="T56" t="n">
-        <v>64.95999999999999</v>
+        <v>34.62</v>
       </c>
       <c r="U56" t="n">
-        <v>61.5</v>
+        <v>34.2</v>
       </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
@@ -4550,1021 +4550,72 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>300409</v>
+        <v>300357</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>道氏技术</t>
+          <t>我武生物</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>26.52</v>
+        <v>26.38</v>
       </c>
       <c r="D57" t="n">
-        <v>-6.02</v>
+        <v>0.08</v>
       </c>
       <c r="E57" t="n">
-        <v>26.79</v>
+        <v>26.28</v>
       </c>
       <c r="F57" t="n">
-        <v>25.77</v>
+        <v>26.15</v>
       </c>
       <c r="G57" t="n">
-        <v>25.52</v>
+        <v>25.51</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.243</v>
+        <v>0.125</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.636</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>76.42</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>70.91</v>
+        <v>69.03</v>
       </c>
       <c r="L57" t="n">
-        <v>87.44</v>
+        <v>64.47</v>
       </c>
       <c r="M57" t="n">
-        <v>53.76</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>51.22</v>
+        <v>57.62</v>
       </c>
       <c r="O57" t="n">
-        <v>49.31</v>
+        <v>50.72</v>
       </c>
       <c r="P57" t="n">
-        <v>5912.58</v>
+        <v>1292.09</v>
       </c>
       <c r="Q57" t="n">
-        <v>3027.44</v>
+        <v>1258.87</v>
       </c>
       <c r="R57" t="n">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="S57" t="n">
-        <v>27.3</v>
+        <v>26.69</v>
       </c>
       <c r="T57" t="n">
-        <v>27.49</v>
+        <v>26.98</v>
       </c>
       <c r="U57" t="n">
-        <v>26.41</v>
+        <v>26.1</v>
       </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2202</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>金风科技</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>25.02</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24.47</v>
-      </c>
-      <c r="F58" t="n">
-        <v>24.28</v>
-      </c>
-      <c r="G58" t="n">
-        <v>26.28</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0.965</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="J58" t="n">
-        <v>46.94</v>
-      </c>
-      <c r="K58" t="n">
-        <v>30.58</v>
-      </c>
-      <c r="L58" t="n">
-        <v>79.68000000000001</v>
-      </c>
-      <c r="M58" t="n">
-        <v>50.43</v>
-      </c>
-      <c r="N58" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>47</v>
-      </c>
-      <c r="P58" t="n">
-        <v>25813.14</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>23761.5</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="S58" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="T58" t="n">
-        <v>25.95</v>
-      </c>
-      <c r="U58" t="n">
-        <v>24.84</v>
-      </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>688066</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>航天宏图</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E59" t="n">
-        <v>19.07</v>
-      </c>
-      <c r="F59" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G59" t="n">
-        <v>19.64</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-1.413</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-1.799</v>
-      </c>
-      <c r="J59" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="K59" t="n">
-        <v>47.12</v>
-      </c>
-      <c r="L59" t="n">
-        <v>91.27</v>
-      </c>
-      <c r="M59" t="n">
-        <v>62.52</v>
-      </c>
-      <c r="N59" t="n">
-        <v>48.24</v>
-      </c>
-      <c r="O59" t="n">
-        <v>42.98</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1984.63</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1152.08</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S59" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="T59" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="U59" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>600990</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>四创电子</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="E60" t="n">
-        <v>23.52</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.87</v>
-      </c>
-      <c r="G60" t="n">
-        <v>22.94</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-0.5629999999999999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-0.902</v>
-      </c>
-      <c r="J60" t="n">
-        <v>79.16</v>
-      </c>
-      <c r="K60" t="n">
-        <v>65.31999999999999</v>
-      </c>
-      <c r="L60" t="n">
-        <v>106.84</v>
-      </c>
-      <c r="M60" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="N60" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="O60" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="P60" t="n">
-        <v>437.33</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>448.34</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="S60" t="n">
-        <v>24</v>
-      </c>
-      <c r="T60" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="U60" t="n">
-        <v>23.64</v>
-      </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>航天电器</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>79.67</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E61" t="n">
-        <v>78.03</v>
-      </c>
-      <c r="F61" t="n">
-        <v>71.45999999999999</v>
-      </c>
-      <c r="G61" t="n">
-        <v>67.45</v>
-      </c>
-      <c r="H61" t="n">
-        <v>5.583</v>
-      </c>
-      <c r="I61" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="J61" t="n">
-        <v>85.11</v>
-      </c>
-      <c r="K61" t="n">
-        <v>80</v>
-      </c>
-      <c r="L61" t="n">
-        <v>95.34</v>
-      </c>
-      <c r="M61" t="n">
-        <v>77.31</v>
-      </c>
-      <c r="N61" t="n">
-        <v>71.17</v>
-      </c>
-      <c r="O61" t="n">
-        <v>66.45</v>
-      </c>
-      <c r="P61" t="n">
-        <v>4082.85</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>3578.62</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S61" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="T61" t="n">
-        <v>82.58</v>
-      </c>
-      <c r="U61" t="n">
-        <v>76.65000000000001</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>600584</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>43.59</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="E62" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="F62" t="n">
-        <v>41.28</v>
-      </c>
-      <c r="G62" t="n">
-        <v>41.07</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-0.345</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-1.024</v>
-      </c>
-      <c r="J62" t="n">
-        <v>78.65000000000001</v>
-      </c>
-      <c r="K62" t="n">
-        <v>68.14</v>
-      </c>
-      <c r="L62" t="n">
-        <v>99.67</v>
-      </c>
-      <c r="M62" t="n">
-        <v>66.29000000000001</v>
-      </c>
-      <c r="N62" t="n">
-        <v>56.23</v>
-      </c>
-      <c r="O62" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="P62" t="n">
-        <v>6806.66</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>5197.98</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S62" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="T62" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="U62" t="n">
-        <v>43.36</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>688295</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>中复神鹰</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>52.48</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E63" t="n">
-        <v>51.64</v>
-      </c>
-      <c r="F63" t="n">
-        <v>51.53</v>
-      </c>
-      <c r="G63" t="n">
-        <v>55.08</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.262</v>
-      </c>
-      <c r="I63" t="n">
-        <v>3.398</v>
-      </c>
-      <c r="J63" t="n">
-        <v>40.46</v>
-      </c>
-      <c r="K63" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="L63" t="n">
-        <v>61.27</v>
-      </c>
-      <c r="M63" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="N63" t="n">
-        <v>54.24</v>
-      </c>
-      <c r="O63" t="n">
-        <v>58.26</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1927.99</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2411.89</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S63" t="n">
-        <v>54.04</v>
-      </c>
-      <c r="T63" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="U63" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>300759</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>康龙化成</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="E64" t="n">
-        <v>31</v>
-      </c>
-      <c r="F64" t="n">
-        <v>30.66</v>
-      </c>
-      <c r="G64" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="J64" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="K64" t="n">
-        <v>77.73999999999999</v>
-      </c>
-      <c r="L64" t="n">
-        <v>73.70999999999999</v>
-      </c>
-      <c r="M64" t="n">
-        <v>73.56</v>
-      </c>
-      <c r="N64" t="n">
-        <v>67.19</v>
-      </c>
-      <c r="O64" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="P64" t="n">
-        <v>4922.12</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3616.74</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S64" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="T64" t="n">
-        <v>32.09</v>
-      </c>
-      <c r="U64" t="n">
-        <v>30.61</v>
-      </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>688621</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>阳光诺和</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E65" t="n">
-        <v>66.70999999999999</v>
-      </c>
-      <c r="F65" t="n">
-        <v>67.12</v>
-      </c>
-      <c r="G65" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="J65" t="n">
-        <v>54.99</v>
-      </c>
-      <c r="K65" t="n">
-        <v>58.72</v>
-      </c>
-      <c r="L65" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="M65" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="N65" t="n">
-        <v>57.19</v>
-      </c>
-      <c r="O65" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="P65" t="n">
-        <v>328.02</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>252.62</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S65" t="n">
-        <v>68.33</v>
-      </c>
-      <c r="T65" t="n">
-        <v>69.06999999999999</v>
-      </c>
-      <c r="U65" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>301333</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>诺思格</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>69.26000000000001</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E66" t="n">
-        <v>67.84</v>
-      </c>
-      <c r="F66" t="n">
-        <v>67.98</v>
-      </c>
-      <c r="G66" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-0.147</v>
-      </c>
-      <c r="J66" t="n">
-        <v>62.34</v>
-      </c>
-      <c r="K66" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="L66" t="n">
-        <v>70.64</v>
-      </c>
-      <c r="M66" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="N66" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="O66" t="n">
-        <v>53.51</v>
-      </c>
-      <c r="P66" t="n">
-        <v>259.39</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>261.46</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="S66" t="n">
-        <v>69.37</v>
-      </c>
-      <c r="T66" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="U66" t="n">
-        <v>66.70999999999999</v>
-      </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>963</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>华东医药</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="E67" t="n">
-        <v>35.52</v>
-      </c>
-      <c r="F67" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="G67" t="n">
-        <v>35.37</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="J67" t="n">
-        <v>39.54</v>
-      </c>
-      <c r="K67" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="L67" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="M67" t="n">
-        <v>51.77</v>
-      </c>
-      <c r="N67" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="O67" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1575.56</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1158.39</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S67" t="n">
-        <v>35.78</v>
-      </c>
-      <c r="T67" t="n">
-        <v>35.93</v>
-      </c>
-      <c r="U67" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>603658</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>安图生物</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E68" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="F68" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="G68" t="n">
-        <v>33.98</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-0.182</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-0.309</v>
-      </c>
-      <c r="J68" t="n">
-        <v>54.57</v>
-      </c>
-      <c r="K68" t="n">
-        <v>61.04</v>
-      </c>
-      <c r="L68" t="n">
-        <v>41.62</v>
-      </c>
-      <c r="M68" t="n">
-        <v>54.65</v>
-      </c>
-      <c r="N68" t="n">
-        <v>50.79</v>
-      </c>
-      <c r="O68" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="P68" t="n">
-        <v>161.83</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>198.64</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="S68" t="n">
-        <v>34.33</v>
-      </c>
-      <c r="T68" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="U68" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>300357</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>我武生物</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E69" t="n">
-        <v>26.28</v>
-      </c>
-      <c r="F69" t="n">
-        <v>26.15</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25.51</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="J69" t="n">
-        <v>67.51000000000001</v>
-      </c>
-      <c r="K69" t="n">
-        <v>69.03</v>
-      </c>
-      <c r="L69" t="n">
-        <v>64.47</v>
-      </c>
-      <c r="M69" t="n">
-        <v>66.48999999999999</v>
-      </c>
-      <c r="N69" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="O69" t="n">
-        <v>50.72</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1292.09</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1258.87</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="S69" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="T69" t="n">
-        <v>26.98</v>
-      </c>
-      <c r="U69" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>688050</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>爱博医疗</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="E70" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="F70" t="n">
-        <v>51.48</v>
-      </c>
-      <c r="G70" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-1.341</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-1.591</v>
-      </c>
-      <c r="J70" t="n">
-        <v>28</v>
-      </c>
-      <c r="K70" t="n">
-        <v>38.32</v>
-      </c>
-      <c r="L70" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="M70" t="n">
-        <v>43.57</v>
-      </c>
-      <c r="N70" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="O70" t="n">
-        <v>38.64</v>
-      </c>
-      <c r="P70" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>159.21</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S70" t="n">
-        <v>51.36</v>
-      </c>
-      <c r="T70" t="n">
-        <v>51.79</v>
-      </c>
-      <c r="U70" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
